--- a/MPs_data.xlsx
+++ b/MPs_data.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t xml:space="preserve">Whey Isolado</t>
   </si>
@@ -169,9 +169,6 @@
     <t xml:space="preserve">Óleo de canola </t>
   </si>
   <si>
-    <t xml:space="preserve">ÓLEO DE GIRASSOL</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADOCANTE STEVIA CRISTAL</t>
   </si>
   <si>
@@ -181,171 +178,15 @@
     <t xml:space="preserve">Custo</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Valor energético (kcal)</t>
   </si>
   <si>
-    <t xml:space="preserve">488.461538461538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">285.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">241.8738</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carboidratos</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0769230769231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Açúcares totais</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Açúcares adicionados</t>
   </si>
   <si>
@@ -355,9 +196,6 @@
     <t xml:space="preserve">Lactose</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sacarose</t>
   </si>
   <si>
@@ -367,9 +205,6 @@
     <t xml:space="preserve">Glicose</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Galactose</t>
   </si>
   <si>
@@ -379,609 +214,183 @@
     <t xml:space="preserve">Proteínas</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1538461538462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ácido Aspártico</t>
   </si>
   <si>
-    <t xml:space="preserve">10.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ácido Glutâmico</t>
   </si>
   <si>
-    <t xml:space="preserve">16.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alanina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2</t>
+    <t xml:space="preserve">Alanina_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arginina_nutriente</t>
   </si>
   <si>
     <t xml:space="preserve">Cistina</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fenilalanina</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Glicina</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Histidina</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2</t>
+    <t xml:space="preserve">Isoleucina_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leucina_nutriente</t>
   </si>
   <si>
     <t xml:space="preserve">Lisina</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metionina</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prolina</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Serina</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tirosina</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Treonina</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Triptofano</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Valina</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gorduras Totais</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gorduras Saturadas</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1538461538462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gorduras Trans</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gorduras Monoinsaturadas</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ômega 9</t>
   </si>
   <si>
     <t xml:space="preserve">Gorduras Poli-insaturadas</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ômega 6</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ômega 3</t>
   </si>
   <si>
     <t xml:space="preserve">Colesterol</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fibras Alimentares</t>
   </si>
   <si>
-    <t xml:space="preserve">65.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fibras soluveis</t>
   </si>
   <si>
-    <t xml:space="preserve">86.97</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fibras insolúveis</t>
   </si>
   <si>
-    <t xml:space="preserve">21.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sódio</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411538461538462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cálcio</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.29412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ferro</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.18235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0034</t>
-  </si>
-  <si>
     <t xml:space="preserve">Potássio</t>
   </si>
   <si>
-    <t xml:space="preserve">12.35294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zinco</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09118</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fosforo</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.05353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780769230769231</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloro</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28759</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cobre</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01139</t>
-  </si>
-  <si>
     <t xml:space="preserve">Magnésio</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37059</t>
-  </si>
-  <si>
     <t xml:space="preserve">Manganês</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03029</t>
-  </si>
-  <si>
     <t xml:space="preserve">Biotina</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518853</t>
-  </si>
-  <si>
     <t xml:space="preserve">Colina</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82353</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cromo</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455588</t>
-  </si>
-  <si>
     <t xml:space="preserve">Flúor</t>
   </si>
   <si>
-    <t xml:space="preserve">0.05324</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ácido Fólico</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00415</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iodo</t>
   </si>
   <si>
-    <t xml:space="preserve">0.001708824</t>
-  </si>
-  <si>
     <t xml:space="preserve">Molibdênio</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592353</t>
-  </si>
-  <si>
     <t xml:space="preserve">Niacinamida</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27059</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ácido Pantotênico</t>
   </si>
   <si>
-    <t xml:space="preserve">0.09594</t>
-  </si>
-  <si>
     <t xml:space="preserve">Selênio</t>
   </si>
   <si>
     <t xml:space="preserve">Vitamina A</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0141489</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vitamina B1</t>
   </si>
   <si>
-    <t xml:space="preserve">0.02065</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vitamina B12</t>
   </si>
   <si>
-    <t xml:space="preserve">0.041676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00000128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00000123076923076923</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vitamina B2</t>
   </si>
   <si>
-    <t xml:space="preserve">0.02388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00107692307692308</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vitamina B6</t>
   </si>
   <si>
     <t xml:space="preserve">Vitamina D3</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00009294</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vitamina E</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106254</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vitamina K1</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00119659</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vitamina C</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88853</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Láurico, g/100g</t>
   </si>
   <si>
@@ -994,63 +403,30 @@
     <t xml:space="preserve">Ác. Palmitoléico, g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Esteárico, g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Oléico, g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Linoléico, g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Linolênico, g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Araquídico, g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Gadoléico, g/100g</t>
   </si>
   <si>
     <t xml:space="preserve">Ác. Behênico,g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ác. Erúcico, g/100g</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pantotenato de cálcio como D-pantotenato de cálcio</t>
   </si>
   <si>
@@ -1063,42 +439,43 @@
     <t xml:space="preserve">D-biotina como D-biotina diluída</t>
   </si>
   <si>
-    <t xml:space="preserve">L-carnitina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-Taurina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ácido Citrico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acessulfame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creatina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hmb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aroma de baunilha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca 30HS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stevia</t>
+    <t xml:space="preserve">L-carnitina_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-Glutamina_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-Taurina_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ácido Citrico_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acessulfame_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creatina_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hmb_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aroma de baunilha_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca 30HS_nutriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stevia_nutriente</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1183,8 +560,12 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1197,6 +578,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1330,249 +715,246 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AN102"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AM102"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.73"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="1"/>
+      <c r="AM1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="O2" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="P2" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="R2" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="S2" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="U2" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="V2" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="X2" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y2" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA2" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB2" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC2" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD2" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE2" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF2" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG2" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH2" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI2" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ2" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK2" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL2" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="AM2" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN2" s="1"/>
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>15.995</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>9.116</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>16.562</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>13.239</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>9.616</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>8.205</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>10.267</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>5.488</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>4.084</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>9.213</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>1.937</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>3.183</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W2" s="5" t="n">
+        <v>2.411</v>
+      </c>
+      <c r="X2" s="5" t="n">
+        <v>0.935</v>
+      </c>
+      <c r="Y2" s="5" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Z2" s="5" t="n">
+        <v>5.068</v>
+      </c>
+      <c r="AA2" s="5" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="AB2" s="5" t="n">
+        <v>6.077</v>
+      </c>
+      <c r="AC2" s="5" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="AD2" s="5" t="n">
+        <v>9.616</v>
+      </c>
+      <c r="AE2" s="5" t="n">
+        <v>2.983</v>
+      </c>
+      <c r="AF2" s="5" t="n">
+        <v>3.617</v>
+      </c>
+      <c r="AG2" s="5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH2" s="5" t="n">
+        <v>7.823</v>
+      </c>
+      <c r="AI2" s="5" t="n">
+        <v>17.147</v>
+      </c>
+      <c r="AJ2" s="5" t="n">
+        <v>3.312</v>
+      </c>
+      <c r="AK2" s="5" t="n">
+        <v>20.221</v>
+      </c>
+      <c r="AL2" s="5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AM2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
+      <c r="A3" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>374</v>
@@ -1595,8 +977,8 @@
       <c r="H3" s="1" t="n">
         <v>288</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>78</v>
+      <c r="I3" s="1" t="n">
+        <v>488.461538461538</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>0</v>
@@ -1622,8 +1004,8 @@
       <c r="Q3" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>79</v>
+      <c r="R3" s="1" t="n">
+        <v>285.3</v>
       </c>
       <c r="S3" s="1" t="n">
         <v>178</v>
@@ -1649,8 +1031,8 @@
       <c r="Z3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" s="1" t="s">
-        <v>80</v>
+      <c r="AA3" s="1" t="n">
+        <v>241.8738</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>0</v>
@@ -1680,25 +1062,22 @@
         <v>742</v>
       </c>
       <c r="AK3" s="1" t="n">
-        <v>739</v>
+        <v>0</v>
       </c>
       <c r="AL3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="AN3" s="1"/>
+      <c r="AM3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>83</v>
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>7.7</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -1715,8 +1094,8 @@
       <c r="H4" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>84</v>
+      <c r="I4" s="1" t="n">
+        <v>38.0769230769231</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>0</v>
@@ -1742,8 +1121,8 @@
       <c r="Q4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>85</v>
+      <c r="R4" s="1" t="n">
+        <v>86.6</v>
       </c>
       <c r="S4" s="1" t="n">
         <v>0</v>
@@ -1769,8 +1148,8 @@
       <c r="Z4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" s="1" t="s">
-        <v>86</v>
+      <c r="AA4" s="1" t="n">
+        <v>59.3</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>0</v>
@@ -1800,25 +1179,22 @@
         <v>18</v>
       </c>
       <c r="AK4" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN4" s="1"/>
+        <v>88.6</v>
+      </c>
+      <c r="AM4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>90</v>
+      <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>5.8</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -1835,8 +1211,8 @@
       <c r="H5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>84</v>
+      <c r="I5" s="1" t="n">
+        <v>38.0769230769231</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>0</v>
@@ -1895,11 +1271,11 @@
       <c r="AB5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>92</v>
+      <c r="AC5" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>2.6</v>
       </c>
       <c r="AE5" s="1" t="n">
         <v>0</v>
@@ -1919,20 +1295,17 @@
       <c r="AJ5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" s="1" t="s">
-        <v>93</v>
+      <c r="AK5" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="1"/>
+      <c r="AM5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>94</v>
+      <c r="A6" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
@@ -2015,11 +1388,11 @@
       <c r="AB6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>92</v>
+      <c r="AC6" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>2.6</v>
       </c>
       <c r="AE6" s="1" t="n">
         <v>0</v>
@@ -2039,20 +1412,17 @@
       <c r="AJ6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AK6" s="1" t="s">
-        <v>93</v>
+      <c r="AK6" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="1"/>
+      <c r="AM6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>95</v>
+      <c r="A7" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
@@ -2165,20 +1535,17 @@
       <c r="AL7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="1"/>
+      <c r="AM7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>97</v>
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>5.4</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>3</v>
@@ -2195,8 +1562,8 @@
       <c r="H8" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>84</v>
+      <c r="I8" s="1" t="n">
+        <v>38.0769230769231</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>0</v>
@@ -2285,14 +1652,11 @@
       <c r="AL8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="1"/>
+      <c r="AM8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>98</v>
+      <c r="A9" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -2405,14 +1769,11 @@
       <c r="AL9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="1"/>
+      <c r="AM9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>99</v>
+      <c r="A10" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0</v>
@@ -2525,20 +1886,17 @@
       <c r="AL10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="1"/>
+      <c r="AM10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>100</v>
+      <c r="A11" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>101</v>
+      <c r="C11" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>0</v>
@@ -2645,20 +2003,17 @@
       <c r="AL11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="1"/>
+      <c r="AM11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>102</v>
+      <c r="A12" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>101</v>
+      <c r="C12" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>0</v>
@@ -2765,14 +2120,11 @@
       <c r="AL12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="1"/>
+      <c r="AM12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>103</v>
+      <c r="A13" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0</v>
@@ -2885,14 +2237,11 @@
       <c r="AL13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="1"/>
+      <c r="AM13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>104</v>
+      <c r="A14" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>88</v>
@@ -2909,14 +2258,14 @@
       <c r="F14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>106</v>
+      <c r="G14" s="1" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>26.1538461538462</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>0</v>
@@ -2942,8 +2291,8 @@
       <c r="Q14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R14" s="1" t="s">
-        <v>107</v>
+      <c r="R14" s="1" t="n">
+        <v>4.4</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>5</v>
@@ -2954,8 +2303,8 @@
       <c r="U14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="1" t="s">
-        <v>108</v>
+      <c r="V14" s="1" t="n">
+        <v>0.8</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>0</v>
@@ -2996,35 +2345,32 @@
       <c r="AI14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ14" s="1" t="s">
-        <v>83</v>
+      <c r="AJ14" s="1" t="n">
+        <v>7.7</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AN14" s="1"/>
+        <v>0.6</v>
+      </c>
+      <c r="AM14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>114</v>
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>10.2</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>0</v>
@@ -3125,26 +2471,23 @@
       <c r="AL15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="1"/>
+      <c r="AM15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>119</v>
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>16.8</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>0</v>
@@ -3245,26 +2588,23 @@
       <c r="AL16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="1"/>
+      <c r="AM16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>124</v>
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>3.8</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>0</v>
@@ -3365,26 +2705,23 @@
       <c r="AL17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="1"/>
+      <c r="AM17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>82</v>
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>6.7</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0</v>
@@ -3485,26 +2822,23 @@
       <c r="AL18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="1"/>
+      <c r="AM18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>130</v>
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1.92</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>131</v>
+      <c r="E19" s="1" t="n">
+        <v>1.1</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>0</v>
@@ -3605,26 +2939,23 @@
       <c r="AL19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="1"/>
+      <c r="AM19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>135</v>
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>4.6</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>0</v>
@@ -3725,26 +3056,23 @@
       <c r="AL20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="1"/>
+      <c r="AM20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>139</v>
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>3.7</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>0</v>
@@ -3845,26 +3173,23 @@
       <c r="AL21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="1"/>
+      <c r="AM21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>143</v>
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>2.3</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>0</v>
@@ -3965,26 +3290,23 @@
       <c r="AL22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="1"/>
+      <c r="AM22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>146</v>
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>4.3</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>0</v>
@@ -4085,26 +3407,23 @@
       <c r="AL23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="1"/>
+      <c r="AM23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>150</v>
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>9.46</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>8.72</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>7.2</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>0</v>
@@ -4205,26 +3524,23 @@
       <c r="AL24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="1"/>
+      <c r="AM24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>153</v>
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>7.36</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>154</v>
+      <c r="E25" s="1" t="n">
+        <v>5.5</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>0</v>
@@ -4325,26 +3641,23 @@
       <c r="AL25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="1"/>
+      <c r="AM25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>131</v>
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>1.1</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>0</v>
@@ -4445,26 +3758,23 @@
       <c r="AL26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="1"/>
+      <c r="AM26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>135</v>
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>4.6</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>0</v>
@@ -4565,26 +3875,23 @@
       <c r="AL27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="1"/>
+      <c r="AM27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>135</v>
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>4.6</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>0</v>
@@ -4685,26 +3992,23 @@
       <c r="AL28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="1"/>
+      <c r="AM28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>170</v>
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>3.3</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>0</v>
@@ -4805,26 +4109,23 @@
       <c r="AL29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="1"/>
+      <c r="AM29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>170</v>
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>3.3</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>0</v>
@@ -4925,26 +4226,23 @@
       <c r="AL30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="1"/>
+      <c r="AM30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>131</v>
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>1.1</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>0</v>
@@ -5045,26 +4343,23 @@
       <c r="AL31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="1"/>
+      <c r="AM31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>107</v>
+      <c r="A32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>4.4</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>0</v>
@@ -5165,17 +4460,14 @@
       <c r="AL32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" s="1"/>
+      <c r="AM32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>183</v>
+      <c r="A33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>7</v>
@@ -5183,8 +4475,8 @@
       <c r="D33" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>184</v>
+      <c r="E33" s="1" t="n">
+        <v>3.1</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>0</v>
@@ -5195,8 +4487,8 @@
       <c r="H33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>106</v>
+      <c r="I33" s="1" t="n">
+        <v>26.1538461538462</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>0</v>
@@ -5222,8 +4514,8 @@
       <c r="Q33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R33" s="1" t="s">
-        <v>185</v>
+      <c r="R33" s="1" t="n">
+        <v>0.62</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>0</v>
@@ -5234,8 +4526,8 @@
       <c r="U33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="1" t="s">
-        <v>186</v>
+      <c r="V33" s="1" t="n">
+        <v>0.1</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>0</v>
@@ -5255,8 +4547,8 @@
       <c r="AB33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="1" t="s">
-        <v>187</v>
+      <c r="AC33" s="1" t="n">
+        <v>0.3</v>
       </c>
       <c r="AD33" s="1" t="n">
         <v>73</v>
@@ -5280,31 +4572,28 @@
         <v>71</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AN33" s="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AM33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>189</v>
+      <c r="A34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>2.8</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>108</v>
+      <c r="E34" s="1" t="n">
+        <v>0.8</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>0</v>
@@ -5315,8 +4604,8 @@
       <c r="H34" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>190</v>
+      <c r="I34" s="1" t="n">
+        <v>16.1538461538462</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>0</v>
@@ -5342,8 +4631,8 @@
       <c r="Q34" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R34" s="1" t="s">
-        <v>191</v>
+      <c r="R34" s="1" t="n">
+        <v>0.23</v>
       </c>
       <c r="S34" s="1" t="n">
         <v>0</v>
@@ -5375,8 +4664,8 @@
       <c r="AB34" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AC34" s="1" t="s">
-        <v>186</v>
+      <c r="AC34" s="1" t="n">
+        <v>0.1</v>
       </c>
       <c r="AD34" s="1" t="n">
         <v>73</v>
@@ -5393,38 +4682,35 @@
       <c r="AH34" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="AI34" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AJ34" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK34" s="1" t="s">
-        <v>194</v>
+      <c r="AI34" s="1" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ34" s="1" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AK34" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="AN34" s="1"/>
+        <v>0.4</v>
+      </c>
+      <c r="AM34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>196</v>
+      <c r="A35" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>195</v>
+      <c r="C35" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>0</v>
@@ -5510,11 +4796,11 @@
       <c r="AG35" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH35" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI35" s="1" t="s">
-        <v>101</v>
+      <c r="AH35" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI35" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="AJ35" s="1" t="n">
         <v>0</v>
@@ -5525,26 +4811,23 @@
       <c r="AL35" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="1"/>
+      <c r="AM35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>200</v>
+      <c r="A36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>0</v>
@@ -5582,8 +4865,8 @@
       <c r="Q36" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R36" s="1" t="s">
-        <v>201</v>
+      <c r="R36" s="1" t="n">
+        <v>0.21</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>0</v>
@@ -5640,22 +4923,19 @@
         <v>42</v>
       </c>
       <c r="AK36" s="1" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL36" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" s="1"/>
+      <c r="AM36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>101</v>
+      <c r="A37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>2</v>
@@ -5765,26 +5045,23 @@
       <c r="AL37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="1"/>
+      <c r="AM37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>158</v>
+      <c r="A38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>1.8</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>0</v>
@@ -5822,8 +5099,8 @@
       <c r="Q38" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R38" s="1" t="s">
-        <v>197</v>
+      <c r="R38" s="1" t="n">
+        <v>0.15</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>0</v>
@@ -5880,25 +5157,22 @@
         <v>21</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="AL38" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="1"/>
+      <c r="AM38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>207</v>
+      <c r="A39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>1.3</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>0</v>
@@ -6005,20 +5279,17 @@
       <c r="AL39" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="1"/>
+      <c r="AM39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>208</v>
+      <c r="A40" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>207</v>
+      <c r="C40" s="1" t="n">
+        <v>1.3</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>0</v>
@@ -6125,20 +5396,17 @@
       <c r="AL40" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" s="1"/>
+      <c r="AM40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>210</v>
+      <c r="A41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>0.0029</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>177</v>
+        <v>0.177</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>0</v>
@@ -6218,8 +5486,8 @@
       <c r="AC41" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AD41" s="1" t="s">
-        <v>211</v>
+      <c r="AD41" s="1" t="n">
+        <v>0.0025</v>
       </c>
       <c r="AE41" s="1" t="n">
         <v>0</v>
@@ -6233,8 +5501,8 @@
       <c r="AH41" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" s="1" t="s">
-        <v>197</v>
+      <c r="AI41" s="1" t="n">
+        <v>0.15</v>
       </c>
       <c r="AJ41" s="1" t="n">
         <v>0</v>
@@ -6245,14 +5513,11 @@
       <c r="AL41" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" s="1"/>
+      <c r="AM41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>212</v>
+      <c r="A42" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>0</v>
@@ -6302,8 +5567,8 @@
       <c r="Q42" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="R42" s="1" t="s">
-        <v>213</v>
+      <c r="R42" s="1" t="n">
+        <v>65.56</v>
       </c>
       <c r="S42" s="1" t="n">
         <v>79</v>
@@ -6314,8 +5579,8 @@
       <c r="U42" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="1" t="s">
-        <v>214</v>
+      <c r="V42" s="1" t="n">
+        <v>88.9</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>75</v>
@@ -6335,8 +5600,8 @@
       <c r="AB42" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AC42" s="1" t="s">
-        <v>215</v>
+      <c r="AC42" s="1" t="n">
+        <v>3.4</v>
       </c>
       <c r="AD42" s="1" t="n">
         <v>0</v>
@@ -6365,14 +5630,11 @@
       <c r="AL42" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" s="1"/>
+      <c r="AM42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>216</v>
+      <c r="A43" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>0</v>
@@ -6434,8 +5696,8 @@
       <c r="U43" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="1" t="s">
-        <v>217</v>
+      <c r="V43" s="1" t="n">
+        <v>86.97</v>
       </c>
       <c r="W43" s="1" t="n">
         <v>0</v>
@@ -6485,14 +5747,11 @@
       <c r="AL43" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" s="1"/>
+      <c r="AM43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>218</v>
+      <c r="A44" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="B44" s="1" t="n">
         <v>0</v>
@@ -6542,8 +5801,8 @@
       <c r="Q44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R44" s="1" t="s">
-        <v>219</v>
+      <c r="R44" s="1" t="n">
+        <v>21.03</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>0</v>
@@ -6554,8 +5813,8 @@
       <c r="U44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="1" t="s">
-        <v>220</v>
+      <c r="V44" s="1" t="n">
+        <v>2.23</v>
       </c>
       <c r="W44" s="1" t="n">
         <v>0</v>
@@ -6605,38 +5864,35 @@
       <c r="AL44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" s="1"/>
+      <c r="AM44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>221</v>
+      <c r="A45" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>148</v>
+        <v>0.148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>158</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>223</v>
+        <v>0.158</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>2.00529</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>448</v>
+        <v>0.448</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>448</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>224</v>
+        <v>0.448</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>0.411538461538462</v>
       </c>
       <c r="J45" s="1" t="n">
         <v>0</v>
@@ -6663,10 +5919,10 @@
         <v>0</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>28</v>
+        <v>0.028</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>467</v>
+        <v>0.467</v>
       </c>
       <c r="T45" s="1" t="n">
         <v>0</v>
@@ -6675,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>191</v>
+        <v>0.191</v>
       </c>
       <c r="W45" s="1" t="n">
         <v>0</v>
@@ -6684,7 +5940,7 @@
         <v>0</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>56</v>
+        <v>0.056</v>
       </c>
       <c r="Z45" s="1" t="n">
         <v>0</v>
@@ -6695,68 +5951,65 @@
       <c r="AB45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AC45" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="AD45" s="1" t="s">
-        <v>226</v>
+      <c r="AC45" s="1" t="n">
+        <v>0.14571</v>
+      </c>
+      <c r="AD45" s="1" t="n">
+        <v>0.19</v>
       </c>
       <c r="AE45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AF45" s="1" t="s">
-        <v>227</v>
+      <c r="AF45" s="1" t="n">
+        <v>0.7</v>
       </c>
       <c r="AG45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH45" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="AI45" s="1" t="s">
-        <v>101</v>
+      <c r="AH45" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI45" s="1" t="n">
+        <v>0.2</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>248</v>
+        <v>0.248</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN45" s="1"/>
+        <v>0.015</v>
+      </c>
+      <c r="AM45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>229</v>
+      <c r="A46" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>452</v>
+        <v>0.452</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>842</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>231</v>
+        <v>0.842</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>10.29412</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>992</v>
+        <v>0.992</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>992</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>232</v>
+        <v>0.992</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>0.95</v>
       </c>
       <c r="J46" s="1" t="n">
         <v>0</v>
@@ -6783,10 +6036,10 @@
         <v>0</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>233</v>
+        <v>0.027</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>1.78</v>
       </c>
       <c r="T46" s="1" t="n">
         <v>0</v>
@@ -6794,8 +6047,8 @@
       <c r="U46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="1" t="s">
-        <v>234</v>
+      <c r="V46" s="1" t="n">
+        <v>0.05547</v>
       </c>
       <c r="W46" s="1" t="n">
         <v>0</v>
@@ -6809,8 +6062,8 @@
       <c r="Z46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AA46" s="1" t="s">
-        <v>235</v>
+      <c r="AA46" s="1" t="n">
+        <v>14.7</v>
       </c>
       <c r="AB46" s="1" t="n">
         <v>0</v>
@@ -6830,8 +6083,8 @@
       <c r="AG46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH46" s="1" t="s">
-        <v>197</v>
+      <c r="AH46" s="1" t="n">
+        <v>0.15</v>
       </c>
       <c r="AI46" s="1" t="n">
         <v>0</v>
@@ -6843,31 +6096,28 @@
         <v>0</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AN46" s="1"/>
+        <v>0.018</v>
+      </c>
+      <c r="AM46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>239</v>
+      <c r="A47" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>0.00033</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>0.0007</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>240</v>
+        <v>0.013</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>0.18235</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>0</v>
@@ -6903,10 +6153,10 @@
         <v>0</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>3</v>
+        <v>0.003</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>5</v>
+        <v>0.005</v>
       </c>
       <c r="T47" s="1" t="n">
         <v>0</v>
@@ -6915,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>2</v>
+        <v>0.002</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>0</v>
@@ -6923,8 +6173,8 @@
       <c r="X47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y47" s="1" t="s">
-        <v>241</v>
+      <c r="Y47" s="1" t="n">
+        <v>0.0034</v>
       </c>
       <c r="Z47" s="1" t="n">
         <v>0</v>
@@ -6965,29 +6215,26 @@
       <c r="AL47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" s="1"/>
+      <c r="AM47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>242</v>
+      <c r="A48" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>326</v>
+        <v>0.326</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>382</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>243</v>
+        <v>0.382</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>12.35294</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>0</v>
@@ -7023,10 +6270,10 @@
         <v>0</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>161</v>
-      </c>
-      <c r="S48" s="1" t="s">
-        <v>244</v>
+        <v>0.161</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>1.27</v>
       </c>
       <c r="T48" s="1" t="n">
         <v>0</v>
@@ -7035,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>124</v>
+        <v>0.124</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>0</v>
@@ -7070,8 +6317,8 @@
       <c r="AG48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AH48" s="1" t="s">
-        <v>245</v>
+      <c r="AH48" s="1" t="n">
+        <v>0.96</v>
       </c>
       <c r="AI48" s="1" t="n">
         <v>0</v>
@@ -7085,29 +6332,26 @@
       <c r="AL48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" s="1"/>
+      <c r="AM48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>247</v>
+      <c r="A49" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>0.0048</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>248</v>
+        <v>0.002</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>0.09118</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>0</v>
@@ -7205,14 +6449,11 @@
       <c r="AL49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" s="1"/>
+      <c r="AM49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>249</v>
+      <c r="A50" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B50" s="1" t="n">
         <v>0</v>
@@ -7220,23 +6461,23 @@
       <c r="C50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>253</v>
+      <c r="D50" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>10.05353</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>0.780769230769231</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>0</v>
@@ -7325,14 +6566,11 @@
       <c r="AL50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" s="1"/>
+      <c r="AM50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>254</v>
+      <c r="A51" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="B51" s="1" t="n">
         <v>0</v>
@@ -7340,14 +6578,14 @@
       <c r="C51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>257</v>
+      <c r="D51" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>3.28759</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>0</v>
@@ -7445,14 +6683,11 @@
       <c r="AL51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" s="1"/>
+      <c r="AM51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>258</v>
+      <c r="A52" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B52" s="1" t="n">
         <v>0</v>
@@ -7463,11 +6698,11 @@
       <c r="D52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>260</v>
+      <c r="E52" s="1" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>0.01139</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>0</v>
@@ -7565,14 +6800,11 @@
       <c r="AL52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" s="1"/>
+      <c r="AM52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>261</v>
+      <c r="A53" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="B53" s="1" t="n">
         <v>0</v>
@@ -7583,11 +6815,11 @@
       <c r="D53" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>262</v>
+      <c r="E53" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>3.37059</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>0</v>
@@ -7685,14 +6917,11 @@
       <c r="AL53" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" s="1"/>
+      <c r="AM53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
-        <v>263</v>
+      <c r="A54" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="B54" s="1" t="n">
         <v>0</v>
@@ -7703,11 +6932,11 @@
       <c r="D54" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>265</v>
+      <c r="E54" s="1" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>0.03029</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>0</v>
@@ -7805,14 +7034,11 @@
       <c r="AL54" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" s="1"/>
+      <c r="AM54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
-        <v>266</v>
+      <c r="A55" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="B55" s="1" t="n">
         <v>0</v>
@@ -7826,8 +7052,8 @@
       <c r="E55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>267</v>
+      <c r="F55" s="1" t="n">
+        <v>0.518853</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>0</v>
@@ -7925,14 +7151,11 @@
       <c r="AL55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" s="1"/>
+      <c r="AM55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
-        <v>268</v>
+      <c r="A56" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="B56" s="1" t="n">
         <v>0</v>
@@ -7946,8 +7169,8 @@
       <c r="E56" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>269</v>
+      <c r="F56" s="1" t="n">
+        <v>5.82353</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>0</v>
@@ -8045,14 +7268,11 @@
       <c r="AL56" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN56" s="1"/>
+      <c r="AM56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>270</v>
+      <c r="A57" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="B57" s="1" t="n">
         <v>0</v>
@@ -8066,8 +7286,8 @@
       <c r="E57" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>271</v>
+      <c r="F57" s="1" t="n">
+        <v>0.455588</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>0</v>
@@ -8165,14 +7385,11 @@
       <c r="AL57" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN57" s="1"/>
+      <c r="AM57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>272</v>
+      <c r="A58" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="B58" s="1" t="n">
         <v>0</v>
@@ -8186,8 +7403,8 @@
       <c r="E58" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>273</v>
+      <c r="F58" s="1" t="n">
+        <v>0.05324</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>0</v>
@@ -8285,14 +7502,11 @@
       <c r="AL58" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN58" s="1"/>
+      <c r="AM58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>274</v>
+      <c r="A59" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="B59" s="1" t="n">
         <v>0</v>
@@ -8306,8 +7520,8 @@
       <c r="E59" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>275</v>
+      <c r="F59" s="1" t="n">
+        <v>0.00415</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>0</v>
@@ -8405,14 +7619,11 @@
       <c r="AL59" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN59" s="1"/>
+      <c r="AM59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>276</v>
+      <c r="A60" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B60" s="1" t="n">
         <v>0</v>
@@ -8426,8 +7637,8 @@
       <c r="E60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>277</v>
+      <c r="F60" s="1" t="n">
+        <v>0.001708824</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>0</v>
@@ -8525,14 +7736,11 @@
       <c r="AL60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" s="1"/>
+      <c r="AM60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
-        <v>278</v>
+      <c r="A61" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="B61" s="1" t="n">
         <v>0</v>
@@ -8546,8 +7754,8 @@
       <c r="E61" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>279</v>
+      <c r="F61" s="1" t="n">
+        <v>0.592353</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>0</v>
@@ -8645,14 +7853,11 @@
       <c r="AL61" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM61" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" s="1"/>
+      <c r="AM61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
-        <v>280</v>
+      <c r="A62" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="B62" s="1" t="n">
         <v>0</v>
@@ -8666,8 +7871,8 @@
       <c r="E62" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>281</v>
+      <c r="F62" s="1" t="n">
+        <v>0.27059</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>0</v>
@@ -8765,14 +7970,11 @@
       <c r="AL62" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM62" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN62" s="1"/>
+      <c r="AM62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>282</v>
+      <c r="A63" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B63" s="1" t="n">
         <v>0</v>
@@ -8786,8 +7988,8 @@
       <c r="E63" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>283</v>
+      <c r="F63" s="1" t="n">
+        <v>0.09594</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>0</v>
@@ -8885,14 +8087,11 @@
       <c r="AL63" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM63" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN63" s="1"/>
+      <c r="AM63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>284</v>
+      <c r="A64" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="B64" s="1" t="n">
         <v>0</v>
@@ -8906,8 +8105,8 @@
       <c r="E64" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>271</v>
+      <c r="F64" s="1" t="n">
+        <v>0.455588</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>0</v>
@@ -9005,14 +8204,11 @@
       <c r="AL64" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM64" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN64" s="1"/>
+      <c r="AM64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>285</v>
+      <c r="A65" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="B65" s="1" t="n">
         <v>0</v>
@@ -9026,8 +8222,8 @@
       <c r="E65" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>286</v>
+      <c r="F65" s="1" t="n">
+        <v>0.0141489</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>0</v>
@@ -9125,14 +8321,11 @@
       <c r="AL65" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN65" s="1"/>
+      <c r="AM65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>287</v>
+      <c r="A66" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B66" s="1" t="n">
         <v>0</v>
@@ -9146,8 +8339,8 @@
       <c r="E66" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>288</v>
+      <c r="F66" s="1" t="n">
+        <v>0.02065</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>0</v>
@@ -9245,14 +8438,11 @@
       <c r="AL66" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM66" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" s="1"/>
+      <c r="AM66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>289</v>
+      <c r="A67" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B67" s="1" t="n">
         <v>0</v>
@@ -9266,17 +8456,17 @@
       <c r="E67" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>292</v>
+      <c r="F67" s="1" t="n">
+        <v>0.041676</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>1.28E-006</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>1.28E-006</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>1.23076923076923E-006</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>0</v>
@@ -9365,14 +8555,11 @@
       <c r="AL67" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM67" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN67" s="1"/>
+      <c r="AM67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>293</v>
+      <c r="A68" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="B68" s="1" t="n">
         <v>0</v>
@@ -9386,17 +8573,17 @@
       <c r="E68" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>296</v>
+      <c r="F68" s="1" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>0.00112</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>0.00112</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>0.00107692307692308</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>0</v>
@@ -9485,14 +8672,11 @@
       <c r="AL68" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM68" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" s="1"/>
+      <c r="AM68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>297</v>
+      <c r="A69" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="B69" s="1" t="n">
         <v>0</v>
@@ -9506,8 +8690,8 @@
       <c r="E69" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>294</v>
+      <c r="F69" s="1" t="n">
+        <v>0.02388</v>
       </c>
       <c r="G69" s="1" t="n">
         <v>0</v>
@@ -9605,14 +8789,11 @@
       <c r="AL69" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM69" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN69" s="1"/>
+      <c r="AM69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>298</v>
+      <c r="A70" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="B70" s="1" t="n">
         <v>0</v>
@@ -9626,8 +8807,8 @@
       <c r="E70" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>299</v>
+      <c r="F70" s="1" t="n">
+        <v>9.294E-005</v>
       </c>
       <c r="G70" s="1" t="n">
         <v>0</v>
@@ -9725,14 +8906,11 @@
       <c r="AL70" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM70" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN70" s="1"/>
+      <c r="AM70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>300</v>
+      <c r="A71" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B71" s="1" t="n">
         <v>0</v>
@@ -9746,8 +8924,8 @@
       <c r="E71" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>301</v>
+      <c r="F71" s="1" t="n">
+        <v>0.106254</v>
       </c>
       <c r="G71" s="1" t="n">
         <v>0</v>
@@ -9845,14 +9023,11 @@
       <c r="AL71" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN71" s="1"/>
+      <c r="AM71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>302</v>
+      <c r="A72" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B72" s="1" t="n">
         <v>0</v>
@@ -9866,8 +9041,8 @@
       <c r="E72" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>303</v>
+      <c r="F72" s="1" t="n">
+        <v>0.00119659</v>
       </c>
       <c r="G72" s="1" t="n">
         <v>0</v>
@@ -9965,14 +9140,11 @@
       <c r="AL72" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM72" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN72" s="1"/>
+      <c r="AM72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>304</v>
+      <c r="A73" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B73" s="1" t="n">
         <v>0</v>
@@ -9986,8 +9158,8 @@
       <c r="E73" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>305</v>
+      <c r="F73" s="1" t="n">
+        <v>0.88853</v>
       </c>
       <c r="G73" s="1" t="n">
         <v>0</v>
@@ -10085,14 +9257,11 @@
       <c r="AL73" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM73" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN73" s="1"/>
+      <c r="AM73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>306</v>
+      <c r="A74" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="B74" s="1" t="n">
         <v>0</v>
@@ -10199,20 +9368,17 @@
       <c r="AJ74" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AK74" s="1" t="s">
-        <v>228</v>
+      <c r="AK74" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL74" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM74" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN74" s="1"/>
+      <c r="AM74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>307</v>
+      <c r="A75" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="B75" s="1" t="n">
         <v>0</v>
@@ -10316,23 +9482,20 @@
       <c r="AI75" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ75" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="AK75" s="1" t="s">
-        <v>186</v>
+      <c r="AJ75" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK75" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL75" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM75" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN75" s="1"/>
+      <c r="AM75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>308</v>
+      <c r="A76" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="B76" s="1" t="n">
         <v>0</v>
@@ -10436,23 +9599,20 @@
       <c r="AI76" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ76" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AK76" s="1" t="s">
-        <v>107</v>
+      <c r="AJ76" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK76" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL76" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN76" s="1"/>
+      <c r="AM76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>309</v>
+      <c r="A77" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="B77" s="1" t="n">
         <v>0</v>
@@ -10556,23 +9716,20 @@
       <c r="AI77" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ77" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="AK77" s="1" t="s">
-        <v>311</v>
+      <c r="AJ77" s="1" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AK77" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL77" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN77" s="1"/>
+      <c r="AM77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
-        <v>312</v>
+      <c r="A78" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="B78" s="1" t="n">
         <v>0</v>
@@ -10676,23 +9833,20 @@
       <c r="AI78" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ78" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="AK78" s="1" t="s">
-        <v>313</v>
+      <c r="AJ78" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK78" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL78" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN78" s="1"/>
+      <c r="AM78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>314</v>
+      <c r="A79" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="B79" s="1" t="n">
         <v>0</v>
@@ -10799,20 +9953,17 @@
       <c r="AJ79" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="AK79" s="1" t="s">
-        <v>315</v>
+      <c r="AK79" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL79" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM79" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN79" s="1"/>
+      <c r="AM79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>316</v>
+      <c r="A80" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B80" s="1" t="n">
         <v>0</v>
@@ -10919,20 +10070,17 @@
       <c r="AJ80" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AK80" s="1" t="s">
-        <v>317</v>
+      <c r="AK80" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL80" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN80" s="1"/>
+      <c r="AM80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>318</v>
+      <c r="A81" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="B81" s="1" t="n">
         <v>0</v>
@@ -11036,23 +10184,20 @@
       <c r="AI81" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ81" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="AK81" s="1" t="s">
-        <v>320</v>
+      <c r="AJ81" s="1" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AK81" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL81" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM81" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN81" s="1"/>
+      <c r="AM81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>321</v>
+      <c r="A82" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B82" s="1" t="n">
         <v>0</v>
@@ -11156,23 +10301,20 @@
       <c r="AI82" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ82" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="AK82" s="1" t="s">
-        <v>201</v>
+      <c r="AJ82" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AK82" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL82" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN82" s="1"/>
+      <c r="AM82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>323</v>
+      <c r="A83" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B83" s="1" t="n">
         <v>0</v>
@@ -11276,23 +10418,20 @@
       <c r="AI83" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK83" s="1" t="s">
-        <v>255</v>
+      <c r="AJ83" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK83" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL83" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN83" s="1"/>
+      <c r="AM83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>324</v>
+      <c r="A84" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B84" s="1" t="n">
         <v>0</v>
@@ -11396,23 +10535,20 @@
       <c r="AI84" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ84" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="AK84" s="1" t="s">
-        <v>326</v>
+      <c r="AJ84" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AK84" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL84" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN84" s="1"/>
+      <c r="AM84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>327</v>
+      <c r="A85" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="B85" s="1" t="n">
         <v>0</v>
@@ -11516,23 +10652,20 @@
       <c r="AI85" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AJ85" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK85" s="1" t="s">
-        <v>328</v>
+      <c r="AJ85" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK85" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AL85" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM85" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN85" s="1"/>
+      <c r="AM85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>282</v>
+      <c r="A86" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="B86" s="1" t="n">
         <v>0</v>
@@ -11546,8 +10679,8 @@
       <c r="E86" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>283</v>
+      <c r="F86" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="G86" s="1" t="n">
         <v>0</v>
@@ -11645,14 +10778,11 @@
       <c r="AL86" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM86" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN86" s="1"/>
+      <c r="AM86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
-        <v>274</v>
+      <c r="A87" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="B87" s="1" t="n">
         <v>0</v>
@@ -11666,8 +10796,8 @@
       <c r="E87" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>275</v>
+      <c r="F87" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="G87" s="1" t="n">
         <v>0</v>
@@ -11765,14 +10895,11 @@
       <c r="AL87" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN87" s="1"/>
+      <c r="AM87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
-        <v>280</v>
+      <c r="A88" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="B88" s="1" t="n">
         <v>0</v>
@@ -11786,8 +10913,8 @@
       <c r="E88" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>281</v>
+      <c r="F88" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="G88" s="1" t="n">
         <v>0</v>
@@ -11885,14 +11012,11 @@
       <c r="AL88" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN88" s="1"/>
+      <c r="AM88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>329</v>
+      <c r="A89" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="B89" s="1" t="n">
         <v>0</v>
@@ -12005,14 +11129,11 @@
       <c r="AL89" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN89" s="1"/>
+      <c r="AM89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>330</v>
+      <c r="A90" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B90" s="1" t="n">
         <v>0</v>
@@ -12054,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P90" s="1" t="n">
         <v>0</v>
@@ -12125,14 +11246,11 @@
       <c r="AL90" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN90" s="1"/>
+      <c r="AM90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>331</v>
+      <c r="A91" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="B91" s="1" t="n">
         <v>0</v>
@@ -12159,7 +11277,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K91" s="1" t="n">
         <v>0</v>
@@ -12245,14 +11363,11 @@
       <c r="AL91" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN91" s="1"/>
+      <c r="AM91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>332</v>
+      <c r="A92" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="B92" s="1" t="n">
         <v>0</v>
@@ -12291,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O92" s="1" t="n">
         <v>0</v>
@@ -12365,14 +11480,11 @@
       <c r="AL92" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM92" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN92" s="1"/>
+      <c r="AM92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>333</v>
+      <c r="A93" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B93" s="1" t="n">
         <v>0</v>
@@ -12414,23 +11526,23 @@
         <v>0</v>
       </c>
       <c r="O93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="U93" s="1" t="n">
         <v>0</v>
       </c>
@@ -12485,14 +11597,11 @@
       <c r="AL93" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN93" s="1"/>
+      <c r="AM93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>8</v>
+      <c r="A94" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="B94" s="1" t="n">
         <v>0</v>
@@ -12519,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="1" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1" t="n">
         <v>0</v>
@@ -12605,14 +11714,11 @@
       <c r="AL94" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN94" s="1"/>
+      <c r="AM94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>334</v>
+      <c r="A95" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="B95" s="1" t="n">
         <v>0</v>
@@ -12651,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="1" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O95" s="1" t="n">
         <v>0</v>
@@ -12687,7 +11793,7 @@
         <v>0</v>
       </c>
       <c r="Z95" s="1" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AA95" s="1" t="n">
         <v>0</v>
@@ -12725,14 +11831,11 @@
       <c r="AL95" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN95" s="1"/>
+      <c r="AM95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
-        <v>335</v>
+      <c r="A96" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="B96" s="1" t="n">
         <v>0</v>
@@ -12789,7 +11892,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="1" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U96" s="1" t="n">
         <v>0</v>
@@ -12810,7 +11913,7 @@
         <v>0</v>
       </c>
       <c r="AA96" s="1" t="n">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="AB96" s="1" t="n">
         <v>0</v>
@@ -12845,14 +11948,11 @@
       <c r="AL96" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM96" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN96" s="1"/>
+      <c r="AM96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>336</v>
+      <c r="A97" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="B97" s="1" t="n">
         <v>0</v>
@@ -12933,7 +12033,7 @@
         <v>0</v>
       </c>
       <c r="AB97" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC97" s="1" t="n">
         <v>0</v>
@@ -12965,14 +12065,11 @@
       <c r="AL97" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN97" s="1"/>
+      <c r="AM97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>337</v>
+      <c r="A98" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="B98" s="1" t="n">
         <v>0</v>
@@ -13047,7 +12144,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="1" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="1" t="n">
         <v>0</v>
@@ -13056,7 +12153,7 @@
         <v>0</v>
       </c>
       <c r="AC98" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD98" s="1" t="n">
         <v>0</v>
@@ -13085,14 +12182,11 @@
       <c r="AL98" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN98" s="1"/>
+      <c r="AM98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
-        <v>338</v>
+      <c r="A99" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B99" s="1" t="n">
         <v>0</v>
@@ -13169,8 +12263,8 @@
       <c r="Z99" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AA99" s="1" t="s">
-        <v>339</v>
+      <c r="AA99" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AB99" s="1" t="n">
         <v>0</v>
@@ -13200,383 +12294,29 @@
         <v>0</v>
       </c>
       <c r="AK99" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL99" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AM99" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN99" s="1"/>
+      <c r="AM99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN100" s="1"/>
+      <c r="AM100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN101" s="1"/>
+      <c r="AM101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL102" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN102" s="1"/>
+      <c r="AM102" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>